--- a/template_create_data.xlsx
+++ b/template_create_data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\gemini-excel-tool\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351543CE-0167-4741-B2EF-7CAF02E275A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="エビデンス(マッピング)" sheetId="1" r:id="rId1"/>
@@ -101,22 +102,31 @@
     <definedName name="てｔｓ" hidden="1">{"管理台帳",#N/A,FALSE,"Sheet1"}</definedName>
     <definedName name="てｔｓ_1" hidden="1">{"管理台帳",#N/A,FALSE,"Sheet1"}</definedName>
     <definedName name="てｔｓ_2" hidden="1">{"管理台帳",#N/A,FALSE,"Sheet1"}</definedName>
-    <definedName name="関連表" hidden="1">#REF!</definedName>
     <definedName name="単品別売上データ２" hidden="1">#REF!</definedName>
     <definedName name="物件Ｓ" hidden="1">{#N/A,#N/A,FALSE,"プログラム一覧（入力）";#N/A,#N/A,FALSE,"プログラム一覧（帳票）";#N/A,#N/A,FALSE,"プログラム一覧（更新）";#N/A,#N/A,FALSE,"プログラム一覧（マスタ保守）";#N/A,#N/A,FALSE,"プログラム一覧（ウインドウ）";#N/A,#N/A,FALSE,"プログラム一覧（共通関数）";#N/A,#N/A,FALSE,"Ｓｙｓｔｅｍ Ｂｏｘ 給与 表一覧";#N/A,#N/A,FALSE,"項目種類一覧";#N/A,#N/A,FALSE,"項目区分一覧 ";#N/A,#N/A,FALSE,"支給処理方法";#N/A,#N/A,FALSE,"控除処理方法"}</definedName>
     <definedName name="物件別原価算入額データ" hidden="1">{#N/A,#N/A,FALSE,"プログラム一覧（入力）";#N/A,#N/A,FALSE,"プログラム一覧（帳票）";#N/A,#N/A,FALSE,"プログラム一覧（更新）";#N/A,#N/A,FALSE,"プログラム一覧（マスタ保守）";#N/A,#N/A,FALSE,"プログラム一覧（ウインドウ）";#N/A,#N/A,FALSE,"プログラム一覧（共通関数）";#N/A,#N/A,FALSE,"Ｓｙｓｔｅｍ Ｂｏｘ 給与 表一覧";#N/A,#N/A,FALSE,"項目種類一覧";#N/A,#N/A,FALSE,"項目区分一覧 ";#N/A,#N/A,FALSE,"支給処理方法";#N/A,#N/A,FALSE,"控除処理方法"}</definedName>
+    <definedName name="関連表" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3409" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="583">
   <si>
     <t>No.3-1-1</t>
     <phoneticPr fontId="1"/>
@@ -1940,12 +1950,15 @@
   <si>
     <t>Fullwidth with 0E/0F</t>
   </si>
+  <si>
+    <t>Fullwidth</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -1956,7 +1969,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -2062,7 +2075,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2111,7 +2124,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2126,17 +2139,8 @@
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2187,7 +2191,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2225,7 +2235,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2263,7 +2279,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2301,7 +2323,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2339,7 +2367,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2377,7 +2411,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2415,7 +2455,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2453,7 +2499,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2491,7 +2543,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2529,7 +2587,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10"/>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2567,7 +2631,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11"/>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2605,7 +2675,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 12"/>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2893,12 +2969,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:CC375"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="56.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -2977,7 +3053,7 @@
     <col min="82" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:81">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2985,7 +3061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:81">
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3170,7 +3246,7 @@
       </c>
       <c r="CC4" s="4"/>
     </row>
-    <row r="5" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:81">
       <c r="C5" s="1" t="s">
         <v>54</v>
       </c>
@@ -3355,7 +3431,7 @@
       </c>
       <c r="CC5" s="5"/>
     </row>
-    <row r="6" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:81">
       <c r="C6" s="1" t="s">
         <v>57</v>
       </c>
@@ -3540,7 +3616,7 @@
       </c>
       <c r="CC6" s="6"/>
     </row>
-    <row r="7" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:81">
       <c r="C7" s="1" t="s">
         <v>59</v>
       </c>
@@ -3725,7 +3801,7 @@
       </c>
       <c r="CC7" s="6"/>
     </row>
-    <row r="8" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:81">
       <c r="C8" s="1" t="s">
         <v>61</v>
       </c>
@@ -3964,7 +4040,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:81">
       <c r="C9" s="1" t="s">
         <v>63</v>
       </c>
@@ -4149,7 +4225,7 @@
       </c>
       <c r="CC9" s="5"/>
     </row>
-    <row r="10" spans="2:81" ht="30" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:81" ht="30">
       <c r="B10" s="8" t="s">
         <v>114</v>
       </c>
@@ -4337,7 +4413,7 @@
       </c>
       <c r="CC10" s="9"/>
     </row>
-    <row r="11" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:81">
       <c r="B11" s="2" t="s">
         <v>162</v>
       </c>
@@ -4525,7 +4601,7 @@
       </c>
       <c r="CC11" s="9"/>
     </row>
-    <row r="12" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:81">
       <c r="B12" s="2" t="s">
         <v>215</v>
       </c>
@@ -4713,7 +4789,7 @@
       </c>
       <c r="CC12" s="9"/>
     </row>
-    <row r="13" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:81">
       <c r="B13" s="2" t="s">
         <v>267</v>
       </c>
@@ -4901,7 +4977,7 @@
       </c>
       <c r="CC13" s="9"/>
     </row>
-    <row r="14" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:81">
       <c r="B14" s="2" t="s">
         <v>319</v>
       </c>
@@ -5089,7 +5165,7 @@
       </c>
       <c r="CC14" s="9"/>
     </row>
-    <row r="15" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:81">
       <c r="B15" s="2" t="s">
         <v>340</v>
       </c>
@@ -5277,7 +5353,7 @@
       </c>
       <c r="CC15" s="9"/>
     </row>
-    <row r="16" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:81">
       <c r="B16" s="2" t="s">
         <v>342</v>
       </c>
@@ -5465,7 +5541,7 @@
       </c>
       <c r="CC16" s="9"/>
     </row>
-    <row r="17" spans="2:81" ht="30" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:81" ht="30">
       <c r="B17" s="8" t="s">
         <v>345</v>
       </c>
@@ -5653,7 +5729,7 @@
       </c>
       <c r="CC17" s="9"/>
     </row>
-    <row r="18" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:81">
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -5689,7 +5765,7 @@
       <c r="BZ18" s="3"/>
       <c r="CC18" s="3"/>
     </row>
-    <row r="19" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:81">
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -5725,7 +5801,7 @@
       <c r="BZ19" s="3"/>
       <c r="CC19" s="3"/>
     </row>
-    <row r="20" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:81">
       <c r="D20" s="3">
         <f t="shared" ref="D20:BO23" si="0">LENB(D10)</f>
         <v>0</v>
@@ -6039,7 +6115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:81">
       <c r="D21" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6353,7 +6429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:81">
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6667,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:81">
       <c r="D23" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6981,7 +7057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:81">
       <c r="D24" s="3">
         <f t="shared" ref="D24:BO27" si="3">LENB(D14)</f>
         <v>0</v>
@@ -7295,7 +7371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:81">
       <c r="D25" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7609,7 +7685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:81">
       <c r="D26" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -7923,7 +7999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:81">
       <c r="D27" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -8237,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:81">
       <c r="B28" s="3" t="s">
         <v>0</v>
       </c>
@@ -8279,7 +8355,7 @@
       <c r="BZ28" s="3"/>
       <c r="CC28" s="3"/>
     </row>
-    <row r="29" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:81">
       <c r="C29" s="16" t="s">
         <v>2</v>
       </c>
@@ -8518,7 +8594,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:81">
       <c r="C30" s="16" t="s">
         <v>54</v>
       </c>
@@ -8757,7 +8833,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="31" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:81">
       <c r="C31" s="16" t="s">
         <v>57</v>
       </c>
@@ -8996,7 +9072,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="32" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:81">
       <c r="C32" s="16" t="s">
         <v>59</v>
       </c>
@@ -9235,7 +9311,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:81">
       <c r="C33" s="16" t="s">
         <v>61</v>
       </c>
@@ -9318,7 +9394,7 @@
       <c r="CB33" s="20"/>
       <c r="CC33" s="18"/>
     </row>
-    <row r="34" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:81">
       <c r="C34" s="16" t="s">
         <v>63</v>
       </c>
@@ -9557,7 +9633,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="35" spans="2:81" ht="30" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:81" ht="30">
       <c r="C35" s="16" t="s">
         <v>569</v>
       </c>
@@ -9567,10 +9643,10 @@
       <c r="E35" s="18" t="s">
         <v>573</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="24" t="s">
         <v>575</v>
       </c>
-      <c r="G35" s="27" t="s">
+      <c r="G35" s="24" t="s">
         <v>576</v>
       </c>
       <c r="H35" s="18"/>
@@ -9641,7 +9717,9 @@
       <c r="AS35" s="18"/>
       <c r="AT35" s="18"/>
       <c r="AU35" s="18"/>
-      <c r="AV35" s="18"/>
+      <c r="AV35" s="18" t="s">
+        <v>582</v>
+      </c>
       <c r="AW35" s="18"/>
       <c r="AX35" s="18"/>
       <c r="AY35" s="18"/>
@@ -9676,11 +9754,11 @@
       <c r="CB35" s="18"/>
       <c r="CC35" s="18"/>
     </row>
-    <row r="36" spans="2:81" ht="30" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:81" ht="30">
       <c r="B36" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="8" t="s">
         <v>115</v>
       </c>
       <c r="D36" s="12" t="s">
@@ -9689,22 +9767,22 @@
       <c r="E36" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F36" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="12" t="s">
         <v>384</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J36" s="23" t="s">
+      <c r="J36" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K36" s="23" t="s">
+      <c r="K36" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L36" s="12" t="s">
@@ -9763,7 +9841,7 @@
       <c r="AG36" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="AH36" s="22" t="s">
+      <c r="AH36" s="12" t="s">
         <v>398</v>
       </c>
       <c r="AI36" s="12" t="s">
@@ -9784,7 +9862,7 @@
       <c r="AN36" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="AO36" s="22" t="s">
+      <c r="AO36" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP36" s="12" t="s">
@@ -9871,7 +9949,7 @@
       <c r="BQ36" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="BR36" s="22" t="s">
+      <c r="BR36" s="12" t="s">
         <v>423</v>
       </c>
       <c r="BS36" s="12" t="s">
@@ -9908,11 +9986,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="37" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:81">
       <c r="B37" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="8" t="s">
         <v>426</v>
       </c>
       <c r="D37" s="12" t="s">
@@ -9924,19 +10002,19 @@
       <c r="F37" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="12" t="s">
         <v>331</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="I37" s="23" t="s">
+      <c r="I37" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J37" s="23" t="s">
+      <c r="J37" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K37" s="23" t="s">
+      <c r="K37" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L37" s="12" t="s">
@@ -9983,10 +10061,10 @@
       <c r="AC37" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="AD37" s="23" t="s">
+      <c r="AD37" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="AE37" s="23" t="s">
+      <c r="AE37" s="21" t="s">
         <v>431</v>
       </c>
       <c r="AF37" s="12" t="s">
@@ -9995,7 +10073,7 @@
       <c r="AG37" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="AH37" s="22" t="s">
+      <c r="AH37" s="12" t="s">
         <v>432</v>
       </c>
       <c r="AI37" s="12" t="s">
@@ -10016,7 +10094,7 @@
       <c r="AN37" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="AO37" s="22" t="s">
+      <c r="AO37" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP37" s="12" t="s">
@@ -10103,7 +10181,7 @@
       <c r="BQ37" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="BR37" s="22" t="s">
+      <c r="BR37" s="12" t="s">
         <v>443</v>
       </c>
       <c r="BS37" s="12" t="s">
@@ -10140,11 +10218,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="38" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:81">
       <c r="B38" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="8" t="s">
         <v>216</v>
       </c>
       <c r="D38" s="12" t="s">
@@ -10156,19 +10234,19 @@
       <c r="F38" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="12" t="s">
         <v>446</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="I38" s="23" t="s">
+      <c r="I38" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J38" s="23" t="s">
+      <c r="J38" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="23" t="s">
+      <c r="K38" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L38" s="12" t="s">
@@ -10215,10 +10293,10 @@
       <c r="AC38" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="AD38" s="23" t="s">
+      <c r="AD38" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="AE38" s="23" t="s">
+      <c r="AE38" s="21" t="s">
         <v>431</v>
       </c>
       <c r="AF38" s="12" t="s">
@@ -10227,7 +10305,7 @@
       <c r="AG38" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="AH38" s="22" t="s">
+      <c r="AH38" s="12" t="s">
         <v>449</v>
       </c>
       <c r="AI38" s="12" t="s">
@@ -10248,7 +10326,7 @@
       <c r="AN38" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="AO38" s="22" t="s">
+      <c r="AO38" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP38" s="12" t="s">
@@ -10284,28 +10362,28 @@
       <c r="AZ38" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="BA38" s="22" t="s">
+      <c r="BA38" s="12" t="s">
         <v>457</v>
       </c>
       <c r="BB38" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="BC38" s="22" t="s">
+      <c r="BC38" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="BD38" s="22" t="s">
+      <c r="BD38" s="12" t="s">
         <v>459</v>
       </c>
       <c r="BE38" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="BF38" s="22" t="s">
+      <c r="BF38" s="12" t="s">
         <v>460</v>
       </c>
-      <c r="BG38" s="22" t="s">
+      <c r="BG38" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="BH38" s="22" t="s">
+      <c r="BH38" s="12" t="s">
         <v>462</v>
       </c>
       <c r="BI38" s="12" t="s">
@@ -10335,7 +10413,7 @@
       <c r="BQ38" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="BR38" s="22" t="s">
+      <c r="BR38" s="12" t="s">
         <v>466</v>
       </c>
       <c r="BS38" s="12" t="s">
@@ -10372,11 +10450,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="39" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:81">
       <c r="B39" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" s="8" t="s">
         <v>469</v>
       </c>
       <c r="D39" s="12" t="s">
@@ -10388,19 +10466,19 @@
       <c r="F39" s="12" t="s">
         <v>470</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="12" t="s">
         <v>13</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="I39" s="23" t="s">
+      <c r="I39" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J39" s="23" t="s">
+      <c r="J39" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K39" s="23" t="s">
+      <c r="K39" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L39" s="12" t="s">
@@ -10447,10 +10525,10 @@
       <c r="AC39" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="AD39" s="23" t="s">
+      <c r="AD39" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="AE39" s="23" t="s">
+      <c r="AE39" s="21" t="s">
         <v>431</v>
       </c>
       <c r="AF39" s="12" t="s">
@@ -10459,7 +10537,7 @@
       <c r="AG39" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="AH39" s="22" t="s">
+      <c r="AH39" s="12" t="s">
         <v>473</v>
       </c>
       <c r="AI39" s="12" t="s">
@@ -10480,7 +10558,7 @@
       <c r="AN39" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="AO39" s="22" t="s">
+      <c r="AO39" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP39" s="12" t="s">
@@ -10516,28 +10594,28 @@
       <c r="AZ39" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="BA39" s="22" t="s">
+      <c r="BA39" s="12" t="s">
         <v>481</v>
       </c>
       <c r="BB39" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="BC39" s="22" t="s">
+      <c r="BC39" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="BD39" s="22" t="s">
+      <c r="BD39" s="12" t="s">
         <v>483</v>
       </c>
       <c r="BE39" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="BF39" s="22" t="s">
+      <c r="BF39" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="BG39" s="22" t="s">
+      <c r="BG39" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="BH39" s="22" t="s">
+      <c r="BH39" s="12" t="s">
         <v>486</v>
       </c>
       <c r="BI39" s="12" t="s">
@@ -10567,7 +10645,7 @@
       <c r="BQ39" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="BR39" s="22" t="s">
+      <c r="BR39" s="12" t="s">
         <v>490</v>
       </c>
       <c r="BS39" s="12" t="s">
@@ -10604,11 +10682,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="40" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:81">
       <c r="B40" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="8" t="s">
         <v>492</v>
       </c>
       <c r="D40" s="12" t="s">
@@ -10620,19 +10698,19 @@
       <c r="F40" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="12" t="s">
         <v>331</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="I40" s="23" t="s">
+      <c r="I40" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J40" s="23" t="s">
+      <c r="J40" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K40" s="23" t="s">
+      <c r="K40" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L40" s="12" t="s">
@@ -10679,10 +10757,10 @@
       <c r="AC40" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="AD40" s="23" t="s">
+      <c r="AD40" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="AE40" s="23" t="s">
+      <c r="AE40" s="21" t="s">
         <v>431</v>
       </c>
       <c r="AF40" s="12" t="s">
@@ -10691,7 +10769,7 @@
       <c r="AG40" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="AH40" s="22" t="s">
+      <c r="AH40" s="12" t="s">
         <v>328</v>
       </c>
       <c r="AI40" s="12" t="s">
@@ -10712,7 +10790,7 @@
       <c r="AN40" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="AO40" s="22" t="s">
+      <c r="AO40" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP40" s="12" t="s">
@@ -10799,7 +10877,7 @@
       <c r="BQ40" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="BR40" s="22" t="s">
+      <c r="BR40" s="12" t="s">
         <v>443</v>
       </c>
       <c r="BS40" s="12" t="s">
@@ -10836,11 +10914,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="41" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:81">
       <c r="B41" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="8" t="s">
         <v>496</v>
       </c>
       <c r="D41" s="12" t="s">
@@ -10852,19 +10930,19 @@
       <c r="F41" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="12" t="s">
         <v>384</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I41" s="23" t="s">
+      <c r="I41" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J41" s="23" t="s">
+      <c r="J41" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="23" t="s">
+      <c r="K41" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L41" s="12" t="s">
@@ -10923,7 +11001,7 @@
       <c r="AG41" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="AH41" s="22" t="s">
+      <c r="AH41" s="12" t="s">
         <v>398</v>
       </c>
       <c r="AI41" s="12" t="s">
@@ -10944,7 +11022,7 @@
       <c r="AN41" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="AO41" s="22" t="s">
+      <c r="AO41" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP41" s="12" t="s">
@@ -11031,7 +11109,7 @@
       <c r="BQ41" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="BR41" s="22" t="s">
+      <c r="BR41" s="12" t="s">
         <v>423</v>
       </c>
       <c r="BS41" s="12" t="s">
@@ -11068,11 +11146,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="42" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:81">
       <c r="B42" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="8" t="s">
         <v>498</v>
       </c>
       <c r="D42" s="12" t="s">
@@ -11084,19 +11162,19 @@
       <c r="F42" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G42" s="12" t="s">
         <v>384</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I42" s="23" t="s">
+      <c r="I42" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J42" s="23" t="s">
+      <c r="J42" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="23" t="s">
+      <c r="K42" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L42" s="12" t="s">
@@ -11155,7 +11233,7 @@
       <c r="AG42" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="AH42" s="22" t="s">
+      <c r="AH42" s="12" t="s">
         <v>398</v>
       </c>
       <c r="AI42" s="12" t="s">
@@ -11176,7 +11254,7 @@
       <c r="AN42" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="AO42" s="22" t="s">
+      <c r="AO42" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP42" s="12" t="s">
@@ -11263,7 +11341,7 @@
       <c r="BQ42" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="BR42" s="22" t="s">
+      <c r="BR42" s="12" t="s">
         <v>423</v>
       </c>
       <c r="BS42" s="12" t="s">
@@ -11300,11 +11378,11 @@
         <v>425</v>
       </c>
     </row>
-    <row r="43" spans="2:81" ht="30" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:81" ht="30">
       <c r="B43" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="8" t="s">
         <v>346</v>
       </c>
       <c r="D43" s="12" t="s">
@@ -11316,19 +11394,19 @@
       <c r="F43" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="12" t="s">
         <v>384</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="I43" s="23" t="s">
+      <c r="I43" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="J43" s="23" t="s">
+      <c r="J43" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="23" t="s">
+      <c r="K43" s="21" t="s">
         <v>60</v>
       </c>
       <c r="L43" s="12" t="s">
@@ -11387,7 +11465,7 @@
       <c r="AG43" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="AH43" s="22" t="s">
+      <c r="AH43" s="12" t="s">
         <v>398</v>
       </c>
       <c r="AI43" s="12" t="s">
@@ -11408,7 +11486,7 @@
       <c r="AN43" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="AO43" s="22" t="s">
+      <c r="AO43" s="12" t="s">
         <v>325</v>
       </c>
       <c r="AP43" s="12" t="s">
@@ -11495,7 +11573,7 @@
       <c r="BQ43" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="BR43" s="22" t="s">
+      <c r="BR43" s="12" t="s">
         <v>423</v>
       </c>
       <c r="BS43" s="12" t="s">
@@ -11532,12 +11610,12 @@
         <v>425</v>
       </c>
     </row>
-    <row r="44" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:81">
       <c r="AY44" s="2" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="45" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:81">
       <c r="D45" s="3">
         <f t="shared" ref="D45:BO48" si="4">LENB(D36)</f>
         <v>4</v>
@@ -11600,183 +11678,183 @@
       </c>
       <c r="S45" s="3">
         <f t="shared" si="4"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T45" s="3">
         <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="U45" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="V45" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="X45" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="Z45" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AD45" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AE45" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AF45" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AH45" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AI45" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AJ45" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AK45" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AL45" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AM45" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AN45" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AO45" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="AP45" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AQ45" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AR45" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AS45" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AT45" s="3">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="U45" s="3">
+      <c r="AU45" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AV45" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AW45" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AX45" s="3">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="AY45" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AZ45" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BA45" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BB45" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BC45" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BD45" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BE45" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BF45" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BG45" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="BH45" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BI45" s="3">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="V45" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="W45" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="X45" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="Y45" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="Z45" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA45" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AC45" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AD45" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AE45" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AF45" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AH45" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AI45" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AJ45" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AK45" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AL45" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AM45" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AN45" s="3">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AO45" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="AP45" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AQ45" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AR45" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AS45" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AT45" s="3">
-        <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="AU45" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AV45" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AW45" s="3">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AX45" s="3">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="AY45" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AZ45" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BA45" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BB45" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BC45" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="BD45" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BE45" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BF45" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="BG45" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="BH45" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BI45" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
       <c r="BJ45" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK45" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL45" s="3">
         <f t="shared" si="4"/>
@@ -11812,7 +11890,7 @@
       </c>
       <c r="BT45" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU45" s="3">
         <f t="shared" si="5"/>
@@ -11851,7 +11929,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:81" s="3" customFormat="1">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="3">
@@ -11916,183 +11994,183 @@
       </c>
       <c r="S46" s="3">
         <f t="shared" si="4"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T46" s="3">
         <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="U46" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="V46" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="W46" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="X46" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="Z46" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB46" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AD46" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AE46" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AF46" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AH46" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AI46" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AJ46" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AK46" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AL46" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AM46" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AN46" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AO46" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="AP46" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AQ46" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AR46" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AS46" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AT46" s="3">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="U46" s="3">
+      <c r="AU46" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AV46" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AW46" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AX46" s="3">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="AY46" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AZ46" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BA46" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BB46" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BC46" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BD46" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BE46" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BF46" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BG46" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="BH46" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BI46" s="3">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="V46" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="W46" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="X46" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="Y46" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="Z46" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA46" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB46" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AC46" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AD46" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AE46" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AF46" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AH46" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AI46" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AJ46" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AK46" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AL46" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AM46" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AN46" s="3">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AO46" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="AP46" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AQ46" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AR46" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AS46" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AT46" s="3">
-        <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="AU46" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AV46" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AW46" s="3">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AX46" s="3">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="AY46" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AZ46" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BA46" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BB46" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BC46" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="BD46" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BE46" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BF46" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="BG46" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="BH46" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BI46" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
       <c r="BJ46" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK46" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL46" s="3">
         <f t="shared" si="4"/>
@@ -12128,7 +12206,7 @@
       </c>
       <c r="BT46" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU46" s="3">
         <f t="shared" si="5"/>
@@ -12167,7 +12245,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:81" s="3" customFormat="1">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="3">
@@ -12232,123 +12310,123 @@
       </c>
       <c r="S47" s="3">
         <f t="shared" si="4"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T47" s="3">
         <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="U47" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="V47" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="W47" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="X47" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="Z47" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AD47" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AE47" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AF47" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AH47" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AI47" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AJ47" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AK47" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AL47" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AM47" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AN47" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AO47" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="AP47" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AQ47" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AR47" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AS47" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AT47" s="3">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="U47" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="V47" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="W47" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="AU47" s="3">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="Y47" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="Z47" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA47" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB47" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AC47" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AD47" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AE47" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AF47" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AH47" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AI47" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AJ47" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AK47" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AL47" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AM47" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AN47" s="3">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AO47" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="AP47" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AQ47" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AR47" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AS47" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AT47" s="3">
+      <c r="AV47" s="3">
         <f t="shared" si="4"/>
         <v>22</v>
-      </c>
-      <c r="AU47" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AV47" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
       </c>
       <c r="AW47" s="3">
         <f t="shared" si="4"/>
@@ -12404,11 +12482,11 @@
       </c>
       <c r="BJ47" s="3">
         <f>LENB(BJ38)</f>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK47" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL47" s="3">
         <f t="shared" si="4"/>
@@ -12444,7 +12522,7 @@
       </c>
       <c r="BT47" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU47" s="3">
         <f t="shared" si="5"/>
@@ -12483,7 +12561,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:81" s="3" customFormat="1">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="3">
@@ -12548,183 +12626,183 @@
       </c>
       <c r="S48" s="3">
         <f t="shared" si="4"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T48" s="3">
         <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="U48" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="V48" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="W48" s="3">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="X48" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="Z48" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB48" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AD48" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AE48" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AF48" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AH48" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AI48" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AJ48" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AK48" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AL48" s="3">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="AM48" s="3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AN48" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AO48" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="AP48" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AQ48" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AR48" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AS48" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AT48" s="3">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="U48" s="3">
+      <c r="AU48" s="3">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AV48" s="3">
+        <f t="shared" si="4"/>
+        <v>22</v>
+      </c>
+      <c r="AW48" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AX48" s="3">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="AY48" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AZ48" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BA48" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BB48" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BC48" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BD48" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BE48" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="BF48" s="3">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="BG48" s="3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="BH48" s="3">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="BI48" s="3">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="V48" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="W48" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="X48" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="Y48" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="Z48" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA48" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB48" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AC48" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AD48" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AE48" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AF48" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AH48" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AI48" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AJ48" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AK48" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AL48" s="3">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="AM48" s="3">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="AN48" s="3">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AO48" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="AP48" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AQ48" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="AR48" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AS48" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AT48" s="3">
-        <f t="shared" si="4"/>
-        <v>22</v>
-      </c>
-      <c r="AU48" s="3">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="AV48" s="3">
-        <f t="shared" si="4"/>
-        <v>42</v>
-      </c>
-      <c r="AW48" s="3">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AX48" s="3">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="AY48" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="AZ48" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BA48" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BB48" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BC48" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="BD48" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BE48" s="3">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="BF48" s="3">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="BG48" s="3">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="BH48" s="3">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="BI48" s="3">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
       <c r="BJ48" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK48" s="3">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL48" s="3">
         <f t="shared" si="4"/>
@@ -12760,7 +12838,7 @@
       </c>
       <c r="BT48" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU48" s="3">
         <f t="shared" si="5"/>
@@ -12799,7 +12877,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:81" s="3" customFormat="1">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="3">
@@ -12864,183 +12942,183 @@
       </c>
       <c r="S49" s="3">
         <f t="shared" si="6"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T49" s="3">
         <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="U49" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="V49" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="W49" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="X49" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="Z49" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AD49" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AE49" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AF49" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AH49" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AI49" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AJ49" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AK49" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AL49" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AM49" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AN49" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AO49" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="AP49" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AQ49" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AR49" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AS49" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AT49" s="3">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="U49" s="3">
+      <c r="AU49" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AV49" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AW49" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AX49" s="3">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="AY49" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AZ49" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BA49" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BB49" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BC49" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BD49" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BE49" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BF49" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BG49" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="BH49" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BI49" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="V49" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="W49" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="X49" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="Y49" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="Z49" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA49" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AB49" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AC49" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AD49" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AE49" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AF49" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AH49" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AI49" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AJ49" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AK49" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AL49" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AM49" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AN49" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AO49" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="AP49" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AQ49" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AR49" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AS49" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AT49" s="3">
-        <f t="shared" si="6"/>
-        <v>22</v>
-      </c>
-      <c r="AU49" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AV49" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AW49" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AX49" s="3">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="AY49" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AZ49" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BA49" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BB49" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BC49" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BD49" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BE49" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BF49" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BG49" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="BH49" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BI49" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
       <c r="BJ49" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK49" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL49" s="3">
         <f t="shared" si="6"/>
@@ -13076,7 +13154,7 @@
       </c>
       <c r="BT49" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU49" s="3">
         <f t="shared" si="5"/>
@@ -13115,7 +13193,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:81" s="3" customFormat="1">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="3">
@@ -13180,183 +13258,183 @@
       </c>
       <c r="S50" s="3">
         <f t="shared" si="6"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T50" s="3">
         <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="U50" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="V50" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="W50" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="X50" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="Z50" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AD50" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AE50" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AF50" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AG50" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AH50" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AI50" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AJ50" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AK50" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AL50" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AM50" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AN50" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AO50" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="AP50" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AQ50" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AR50" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AS50" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AT50" s="3">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="U50" s="3">
+      <c r="AU50" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AV50" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AW50" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AX50" s="3">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="AY50" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AZ50" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BA50" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BB50" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BC50" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BD50" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BE50" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BF50" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BG50" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="BH50" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BI50" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="V50" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="W50" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="X50" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="Y50" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="Z50" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA50" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AB50" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AC50" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AD50" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AE50" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AF50" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AG50" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AH50" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AI50" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AJ50" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AK50" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AL50" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AM50" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AN50" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AO50" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="AP50" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AQ50" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AR50" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AS50" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AT50" s="3">
-        <f t="shared" si="6"/>
-        <v>22</v>
-      </c>
-      <c r="AU50" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AV50" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AW50" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AX50" s="3">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="AY50" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AZ50" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BA50" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BB50" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BC50" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BD50" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BE50" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BF50" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BG50" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="BH50" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BI50" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
       <c r="BJ50" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK50" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL50" s="3">
         <f t="shared" si="6"/>
@@ -13392,7 +13470,7 @@
       </c>
       <c r="BT50" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU50" s="3">
         <f t="shared" si="5"/>
@@ -13431,7 +13509,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:81" s="3" customFormat="1">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="3">
@@ -13496,183 +13574,183 @@
       </c>
       <c r="S51" s="3">
         <f t="shared" si="6"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T51" s="3">
         <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="U51" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="V51" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="W51" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="X51" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="Z51" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AD51" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AE51" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AF51" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AG51" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AH51" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AI51" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AJ51" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AK51" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AL51" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AM51" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AN51" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AO51" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="AP51" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AQ51" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AR51" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AS51" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AT51" s="3">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="U51" s="3">
+      <c r="AU51" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AV51" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AW51" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AX51" s="3">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="AY51" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AZ51" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BA51" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BB51" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BC51" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BD51" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BE51" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BF51" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BG51" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="BH51" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BI51" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="V51" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="W51" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="X51" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="Y51" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="Z51" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA51" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AB51" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AC51" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AD51" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AE51" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AF51" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AG51" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AH51" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AI51" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AJ51" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AK51" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AL51" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AM51" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AN51" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AO51" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="AP51" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AQ51" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AR51" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AS51" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AT51" s="3">
-        <f t="shared" si="6"/>
-        <v>22</v>
-      </c>
-      <c r="AU51" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AV51" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AW51" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AX51" s="3">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="AY51" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AZ51" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BA51" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BB51" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BC51" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BD51" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BE51" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BF51" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BG51" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="BH51" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BI51" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
       <c r="BJ51" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK51" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL51" s="3">
         <f t="shared" si="6"/>
@@ -13708,7 +13786,7 @@
       </c>
       <c r="BT51" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU51" s="3">
         <f t="shared" si="5"/>
@@ -13747,7 +13825,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:81" s="3" customFormat="1">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="3">
@@ -13812,183 +13890,183 @@
       </c>
       <c r="S52" s="3">
         <f t="shared" si="6"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T52" s="3">
         <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="U52" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="V52" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="W52" s="3">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="X52" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="Z52" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AD52" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AE52" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AF52" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AH52" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AI52" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AJ52" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AK52" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AL52" s="3">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="AM52" s="3">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AN52" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AO52" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="AP52" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AQ52" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AR52" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AS52" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AT52" s="3">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="U52" s="3">
+      <c r="AU52" s="3">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="AV52" s="3">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="AW52" s="3">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="AX52" s="3">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="AY52" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="AZ52" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BA52" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BB52" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BC52" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BD52" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BE52" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="BF52" s="3">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="BG52" s="3">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="BH52" s="3">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="BI52" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="W52" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="X52" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="Y52" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="Z52" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AD52" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AE52" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AF52" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AH52" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AI52" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AJ52" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AK52" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AL52" s="3">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="AM52" s="3">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AN52" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AO52" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="AP52" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AQ52" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AR52" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AS52" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AT52" s="3">
-        <f t="shared" si="6"/>
-        <v>22</v>
-      </c>
-      <c r="AU52" s="3">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AV52" s="3">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-      <c r="AW52" s="3">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="AX52" s="3">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="AY52" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AZ52" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BA52" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BB52" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BC52" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BD52" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BE52" s="3">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="BF52" s="3">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="BG52" s="3">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="BH52" s="3">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="BI52" s="3">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
       <c r="BJ52" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK52" s="3">
         <f t="shared" si="6"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL52" s="3">
         <f t="shared" si="6"/>
@@ -14024,7 +14102,7 @@
       </c>
       <c r="BT52" s="3">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU52" s="3">
         <f t="shared" si="5"/>
@@ -14063,490 +14141,490 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:81" s="3" customFormat="1">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:81" s="3" customFormat="1">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="55" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:81" s="3" customFormat="1">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:81" s="3" customFormat="1">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:81" s="3" customFormat="1">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:81" s="3" customFormat="1">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:81" s="3" customFormat="1">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:81" s="3" customFormat="1">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:81" s="3" customFormat="1">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:81" s="3" customFormat="1">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:81" s="3" customFormat="1">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="2:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:81" s="3" customFormat="1">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:3" s="3" customFormat="1">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:3" s="3" customFormat="1">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:3" s="3" customFormat="1">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:3" s="3" customFormat="1">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:3" s="3" customFormat="1">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:3" s="3" customFormat="1">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:3" s="3" customFormat="1">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:3" s="3" customFormat="1">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:3" s="3" customFormat="1">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:3" s="3" customFormat="1">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:3" s="3" customFormat="1">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:3" s="3" customFormat="1">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:3" s="3" customFormat="1">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:3" s="3" customFormat="1">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:3" s="3" customFormat="1">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:3" s="3" customFormat="1">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:4" s="3" customFormat="1">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:4" s="3" customFormat="1">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:4" s="3" customFormat="1">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:4" s="3" customFormat="1">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:4" s="3" customFormat="1">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:4" s="3" customFormat="1">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="87" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:4" s="3" customFormat="1">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:4" s="3" customFormat="1">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:4" s="3" customFormat="1">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:4" s="3" customFormat="1">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:4" s="3" customFormat="1">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:4" s="3" customFormat="1">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:4" s="3" customFormat="1">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:4" s="3" customFormat="1">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:4" s="3" customFormat="1">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:4" s="3" customFormat="1">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
     </row>
-    <row r="97" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:3" s="3" customFormat="1">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
     </row>
-    <row r="98" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:3" s="3" customFormat="1">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:3" s="3" customFormat="1">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
     </row>
-    <row r="100" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:3" s="3" customFormat="1">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
     </row>
-    <row r="101" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:3" s="3" customFormat="1">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
     </row>
-    <row r="102" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:3" s="3" customFormat="1">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
     </row>
-    <row r="103" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:3" s="3" customFormat="1">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
     </row>
-    <row r="104" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:3" s="3" customFormat="1">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
     </row>
-    <row r="105" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:3" s="3" customFormat="1">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
     </row>
-    <row r="106" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:3" s="3" customFormat="1">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
     </row>
-    <row r="107" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:3" s="3" customFormat="1">
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
     </row>
-    <row r="108" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:3" s="3" customFormat="1">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
     </row>
-    <row r="109" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:3" s="3" customFormat="1">
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
     </row>
-    <row r="110" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:3" s="3" customFormat="1">
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
     </row>
-    <row r="111" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:3" s="3" customFormat="1">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
     </row>
-    <row r="112" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:3" s="3" customFormat="1">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
     </row>
-    <row r="113" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="2:11" s="3" customFormat="1">
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
     </row>
-    <row r="114" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="2:11" s="3" customFormat="1">
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
     </row>
-    <row r="115" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="2:11" s="3" customFormat="1">
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
     </row>
-    <row r="116" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="2:11" s="3" customFormat="1">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
     </row>
-    <row r="117" spans="2:11" s="3" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="2:11" s="3" customFormat="1" ht="90" customHeight="1">
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="28" t="s">
+      <c r="D117" s="25" t="s">
         <v>502</v>
       </c>
-      <c r="E117" s="28"/>
-      <c r="F117" s="28"/>
-      <c r="G117" s="28"/>
-      <c r="H117" s="28"/>
-      <c r="I117" s="28"/>
-      <c r="J117" s="28"/>
-      <c r="K117" s="28"/>
+      <c r="E117" s="25"/>
+      <c r="F117" s="25"/>
+      <c r="G117" s="25"/>
+      <c r="H117" s="25"/>
+      <c r="I117" s="25"/>
+      <c r="J117" s="25"/>
+      <c r="K117" s="25"/>
     </row>
-    <row r="118" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:11" s="3" customFormat="1">
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
     </row>
-    <row r="119" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:11" s="3" customFormat="1">
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
     </row>
-    <row r="120" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:11" s="3" customFormat="1">
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
     </row>
-    <row r="121" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:11" s="3" customFormat="1">
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="122" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:11" s="3" customFormat="1">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
     </row>
-    <row r="123" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="2:11" s="3" customFormat="1">
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
     </row>
-    <row r="124" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="2:11" s="3" customFormat="1">
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
     </row>
-    <row r="125" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="2:11" s="3" customFormat="1">
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
     </row>
-    <row r="126" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="2:11" s="3" customFormat="1">
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
     </row>
-    <row r="127" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:11" s="3" customFormat="1">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
     </row>
-    <row r="128" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="2:11" s="3" customFormat="1">
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
     </row>
-    <row r="129" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="2:3" s="3" customFormat="1">
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
     </row>
-    <row r="130" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="2:3" s="3" customFormat="1">
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
     </row>
-    <row r="131" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="2:3" s="3" customFormat="1">
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
     </row>
-    <row r="132" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="2:3" s="3" customFormat="1">
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
     </row>
-    <row r="133" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="2:3" s="3" customFormat="1">
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
     </row>
-    <row r="134" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="2:3" s="3" customFormat="1">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
     </row>
-    <row r="135" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="2:3" s="3" customFormat="1">
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
     </row>
-    <row r="136" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="2:3" s="3" customFormat="1">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
     </row>
-    <row r="137" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="2:3" s="3" customFormat="1">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
     </row>
-    <row r="138" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="2:3" s="3" customFormat="1">
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
     </row>
-    <row r="139" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="2:3" s="3" customFormat="1">
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
     </row>
-    <row r="140" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="2:3" s="3" customFormat="1">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
     </row>
-    <row r="141" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="2:3" s="3" customFormat="1">
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
     </row>
-    <row r="142" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="2:3" s="3" customFormat="1">
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
     </row>
-    <row r="143" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="2:3" s="3" customFormat="1">
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
     </row>
-    <row r="144" spans="2:3" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="2:3" s="3" customFormat="1">
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
     </row>
-    <row r="145" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4" s="3" customFormat="1">
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
     </row>
-    <row r="146" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4" s="3" customFormat="1">
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
     </row>
-    <row r="147" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4" s="3" customFormat="1">
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
     </row>
-    <row r="148" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4" s="3" customFormat="1">
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="149" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4" s="3" customFormat="1">
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
     </row>
-    <row r="150" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4" s="3" customFormat="1">
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
     </row>
-    <row r="151" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4" s="3" customFormat="1">
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
     </row>
-    <row r="152" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="2:4" s="3" customFormat="1">
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
     </row>
-    <row r="153" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4" s="3" customFormat="1">
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
     </row>
-    <row r="154" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4" s="3" customFormat="1">
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
     </row>
-    <row r="155" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4" s="3" customFormat="1">
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
     </row>
-    <row r="156" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4" s="3" customFormat="1">
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
     </row>
-    <row r="157" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4" s="3" customFormat="1">
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
     </row>
-    <row r="158" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4" s="3" customFormat="1">
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
     </row>
-    <row r="159" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4" s="3" customFormat="1">
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
     </row>
-    <row r="160" spans="2:4" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="2:4" s="3" customFormat="1">
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
     </row>
-    <row r="161" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:81" s="3" customFormat="1">
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
     </row>
-    <row r="162" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:81" s="3" customFormat="1">
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
     </row>
-    <row r="163" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:81" s="3" customFormat="1">
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
     </row>
-    <row r="164" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:81" s="3" customFormat="1">
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
     </row>
-    <row r="165" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:81" s="3" customFormat="1">
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
     </row>
-    <row r="166" spans="1:81" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:81" s="1" customFormat="1">
       <c r="A166" s="1" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="167" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:81" s="3" customFormat="1">
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
     </row>
-    <row r="168" spans="1:81" s="3" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:81" s="3" customFormat="1">
       <c r="C168" s="3" t="s">
         <v>1</v>
       </c>
@@ -14629,7 +14707,7 @@
       <c r="CB168" s="2"/>
       <c r="CC168" s="2"/>
     </row>
-    <row r="169" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:81">
       <c r="C169" s="1" t="s">
         <v>2</v>
       </c>
@@ -14814,7 +14892,7 @@
       </c>
       <c r="CC169" s="4"/>
     </row>
-    <row r="170" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:81">
       <c r="C170" s="1" t="s">
         <v>54</v>
       </c>
@@ -14999,7 +15077,7 @@
       </c>
       <c r="CC170" s="5"/>
     </row>
-    <row r="171" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:81">
       <c r="C171" s="1" t="s">
         <v>57</v>
       </c>
@@ -15184,7 +15262,7 @@
       </c>
       <c r="CC171" s="6"/>
     </row>
-    <row r="172" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:81">
       <c r="C172" s="1" t="s">
         <v>59</v>
       </c>
@@ -15369,7 +15447,7 @@
       </c>
       <c r="CC172" s="6"/>
     </row>
-    <row r="173" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:81">
       <c r="C173" s="1" t="s">
         <v>61</v>
       </c>
@@ -15608,7 +15686,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="174" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:81">
       <c r="C174" s="1" t="s">
         <v>63</v>
       </c>
@@ -15793,7 +15871,7 @@
       </c>
       <c r="CC174" s="5"/>
     </row>
-    <row r="175" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:81">
       <c r="B175" s="2" t="s">
         <v>506</v>
       </c>
@@ -15978,7 +16056,7 @@
       </c>
       <c r="CC175" s="9"/>
     </row>
-    <row r="176" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:81">
       <c r="B176" s="2" t="s">
         <v>509</v>
       </c>
@@ -16163,10 +16241,10 @@
       </c>
       <c r="CC176" s="9"/>
     </row>
-    <row r="178" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:81">
       <c r="E178" s="3"/>
     </row>
-    <row r="179" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:81">
       <c r="D179" s="3">
         <f>LENB(D175)</f>
         <v>0</v>
@@ -16480,7 +16558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:81">
       <c r="E180" s="3">
         <f>LENB(E176)</f>
         <v>4</v>
@@ -16790,7 +16868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="184" spans="2:81">
       <c r="C184" s="3" t="s">
         <v>348</v>
       </c>
@@ -16829,7 +16907,7 @@
       <c r="BZ184" s="3"/>
       <c r="CC184" s="3"/>
     </row>
-    <row r="185" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:81">
       <c r="C185" s="16" t="s">
         <v>2</v>
       </c>
@@ -17068,7 +17146,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="186" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:81">
       <c r="C186" s="16" t="s">
         <v>54</v>
       </c>
@@ -17307,7 +17385,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="187" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:81">
       <c r="C187" s="16" t="s">
         <v>57</v>
       </c>
@@ -17546,7 +17624,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="188" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="188" spans="2:81">
       <c r="C188" s="16" t="s">
         <v>59</v>
       </c>
@@ -17785,7 +17863,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="189" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:81">
       <c r="C189" s="16" t="s">
         <v>61</v>
       </c>
@@ -17868,7 +17946,7 @@
       <c r="CB189" s="20"/>
       <c r="CC189" s="18"/>
     </row>
-    <row r="190" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:81">
       <c r="C190" s="16" t="s">
         <v>63</v>
       </c>
@@ -18107,7 +18185,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:81">
       <c r="B191" s="2" t="s">
         <v>506</v>
       </c>
@@ -18117,28 +18195,28 @@
       <c r="E191" s="14" t="s">
         <v>497</v>
       </c>
-      <c r="F191" s="22" t="s">
+      <c r="F191" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="G191" s="22" t="s">
+      <c r="G191" s="12" t="s">
         <v>518</v>
       </c>
       <c r="H191" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I191" s="25" t="s">
+      <c r="I191" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J191" s="25" t="s">
+      <c r="J191" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="K191" s="25" t="s">
+      <c r="K191" s="22" t="s">
         <v>60</v>
       </c>
       <c r="L191" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="M191" s="22" t="s">
+      <c r="M191" s="12" t="s">
         <v>386</v>
       </c>
       <c r="N191" s="14" t="s">
@@ -18156,10 +18234,10 @@
       <c r="R191" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="S191" s="22" t="s">
+      <c r="S191" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="T191" s="22" t="s">
+      <c r="T191" s="12" t="s">
         <v>390</v>
       </c>
       <c r="U191" s="14" t="s">
@@ -18174,7 +18252,7 @@
       <c r="X191" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="Y191" s="22" t="s">
+      <c r="Y191" s="12" t="s">
         <v>394</v>
       </c>
       <c r="Z191" s="14" t="s">
@@ -18183,10 +18261,10 @@
       <c r="AA191" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="AB191" s="22" t="s">
+      <c r="AB191" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="AC191" s="22" t="s">
+      <c r="AC191" s="12" t="s">
         <v>395</v>
       </c>
       <c r="AD191" s="14" t="s">
@@ -18225,25 +18303,25 @@
       <c r="AO191" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="AP191" s="22" t="s">
+      <c r="AP191" s="12" t="s">
         <v>389</v>
       </c>
       <c r="AQ191" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="AR191" s="22" t="s">
+      <c r="AR191" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="AS191" s="22" t="s">
+      <c r="AS191" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="AT191" s="22" t="s">
+      <c r="AT191" s="12" t="s">
         <v>408</v>
       </c>
       <c r="AU191" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="AV191" s="22" t="s">
+      <c r="AV191" s="12" t="s">
         <v>394</v>
       </c>
       <c r="AW191" s="14" t="s">
@@ -18285,10 +18363,10 @@
       <c r="BI191" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="BJ191" s="22" t="s">
+      <c r="BJ191" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="BK191" s="22" t="s">
+      <c r="BK191" s="12" t="s">
         <v>419</v>
       </c>
       <c r="BL191" s="14" t="s">
@@ -18309,13 +18387,13 @@
       <c r="BQ191" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="BR191" s="22" t="s">
+      <c r="BR191" s="12" t="s">
         <v>519</v>
       </c>
       <c r="BS191" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="BT191" s="22" t="s">
+      <c r="BT191" s="12" t="s">
         <v>424</v>
       </c>
       <c r="BU191" s="14" t="s">
@@ -18346,7 +18424,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="192" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:81">
       <c r="B192" s="2" t="s">
         <v>509</v>
       </c>
@@ -18356,28 +18434,28 @@
       <c r="E192" s="14" t="s">
         <v>497</v>
       </c>
-      <c r="F192" s="22" t="s">
+      <c r="F192" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="G192" s="22" t="s">
+      <c r="G192" s="12" t="s">
         <v>518</v>
       </c>
       <c r="H192" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I192" s="25" t="s">
+      <c r="I192" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J192" s="25" t="s">
+      <c r="J192" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="K192" s="25" t="s">
+      <c r="K192" s="22" t="s">
         <v>60</v>
       </c>
       <c r="L192" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="M192" s="22" t="s">
+      <c r="M192" s="12" t="s">
         <v>520</v>
       </c>
       <c r="N192" s="14" t="s">
@@ -18395,10 +18473,10 @@
       <c r="R192" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="S192" s="22" t="s">
+      <c r="S192" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="T192" s="22" t="s">
+      <c r="T192" s="12" t="s">
         <v>390</v>
       </c>
       <c r="U192" s="14" t="s">
@@ -18413,7 +18491,7 @@
       <c r="X192" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="Y192" s="22" t="s">
+      <c r="Y192" s="12" t="s">
         <v>521</v>
       </c>
       <c r="Z192" s="14" t="s">
@@ -18422,10 +18500,10 @@
       <c r="AA192" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="AB192" s="22" t="s">
+      <c r="AB192" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="AC192" s="22" t="s">
+      <c r="AC192" s="12" t="s">
         <v>522</v>
       </c>
       <c r="AD192" s="14" t="s">
@@ -18464,25 +18542,25 @@
       <c r="AO192" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="AP192" s="22" t="s">
+      <c r="AP192" s="12" t="s">
         <v>389</v>
       </c>
       <c r="AQ192" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="AR192" s="22" t="s">
+      <c r="AR192" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="AS192" s="22" t="s">
+      <c r="AS192" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="AT192" s="22" t="s">
+      <c r="AT192" s="12" t="s">
         <v>408</v>
       </c>
       <c r="AU192" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="AV192" s="22" t="s">
+      <c r="AV192" s="12" t="s">
         <v>525</v>
       </c>
       <c r="AW192" s="14" t="s">
@@ -18524,10 +18602,10 @@
       <c r="BI192" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="BJ192" s="22" t="s">
+      <c r="BJ192" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="BK192" s="22" t="s">
+      <c r="BK192" s="12" t="s">
         <v>419</v>
       </c>
       <c r="BL192" s="14" t="s">
@@ -18548,13 +18626,13 @@
       <c r="BQ192" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="BR192" s="22" t="s">
+      <c r="BR192" s="12" t="s">
         <v>519</v>
       </c>
       <c r="BS192" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="BT192" s="22" t="s">
+      <c r="BT192" s="12" t="s">
         <v>527</v>
       </c>
       <c r="BU192" s="14" t="s">
@@ -18585,7 +18663,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="195" spans="3:81" x14ac:dyDescent="0.15">
+    <row r="195" spans="3:81">
       <c r="D195" s="3">
         <f>LENB(D191)</f>
         <v>4</v>
@@ -18624,7 +18702,7 @@
       </c>
       <c r="M195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="N195" s="3">
         <f t="shared" si="10"/>
@@ -18648,11 +18726,11 @@
       </c>
       <c r="S195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T195" s="3">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U195" s="3">
         <f t="shared" si="10"/>
@@ -18672,7 +18750,7 @@
       </c>
       <c r="Y195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="Z195" s="3">
         <f t="shared" si="10"/>
@@ -18684,11 +18762,11 @@
       </c>
       <c r="AB195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AC195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AD195" s="3">
         <f t="shared" si="10"/>
@@ -18740,7 +18818,7 @@
       </c>
       <c r="AP195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AQ195" s="3">
         <f t="shared" si="10"/>
@@ -18748,15 +18826,15 @@
       </c>
       <c r="AR195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AS195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AT195" s="3">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AU195" s="3">
         <f t="shared" si="10"/>
@@ -18764,7 +18842,7 @@
       </c>
       <c r="AV195" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AW195" s="3">
         <f t="shared" si="10"/>
@@ -18820,11 +18898,11 @@
       </c>
       <c r="BJ195" s="3">
         <f t="shared" si="10"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK195" s="3">
         <f t="shared" si="10"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL195" s="3">
         <f t="shared" si="10"/>
@@ -18860,7 +18938,7 @@
       </c>
       <c r="BT195" s="3">
         <f t="shared" si="11"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU195" s="3">
         <f t="shared" si="11"/>
@@ -18899,7 +18977,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="3:81" x14ac:dyDescent="0.15">
+    <row r="196" spans="3:81">
       <c r="D196" s="3">
         <f>LENB(D192)</f>
         <v>4</v>
@@ -18938,7 +19016,7 @@
       </c>
       <c r="M196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="N196" s="3">
         <f t="shared" si="10"/>
@@ -18962,11 +19040,11 @@
       </c>
       <c r="S196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T196" s="3">
         <f t="shared" si="10"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U196" s="3">
         <f t="shared" si="10"/>
@@ -18986,7 +19064,7 @@
       </c>
       <c r="Y196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="Z196" s="3">
         <f t="shared" si="10"/>
@@ -18998,11 +19076,11 @@
       </c>
       <c r="AB196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AC196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AD196" s="3">
         <f t="shared" si="10"/>
@@ -19054,7 +19132,7 @@
       </c>
       <c r="AP196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AQ196" s="3">
         <f t="shared" si="10"/>
@@ -19062,15 +19140,15 @@
       </c>
       <c r="AR196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AS196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AT196" s="3">
         <f t="shared" si="10"/>
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AU196" s="3">
         <f t="shared" si="10"/>
@@ -19078,7 +19156,7 @@
       </c>
       <c r="AV196" s="3">
         <f t="shared" si="10"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AW196" s="3">
         <f t="shared" si="10"/>
@@ -19134,11 +19212,11 @@
       </c>
       <c r="BJ196" s="3">
         <f t="shared" si="10"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK196" s="3">
         <f t="shared" si="10"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL196" s="3">
         <f t="shared" si="10"/>
@@ -19174,7 +19252,7 @@
       </c>
       <c r="BT196" s="3">
         <f t="shared" si="11"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU196" s="3">
         <f t="shared" si="11"/>
@@ -19213,45 +19291,45 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="3:81" x14ac:dyDescent="0.15">
+    <row r="200" spans="3:81">
       <c r="C200" s="2" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="219" spans="3:3">
       <c r="C219" s="2" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="240" spans="3:18" ht="117" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C240" s="29" t="s">
+    <row r="240" spans="3:18" ht="117" customHeight="1">
+      <c r="C240" s="26" t="s">
         <v>528</v>
       </c>
-      <c r="D240" s="29"/>
-      <c r="E240" s="29"/>
-      <c r="F240" s="29"/>
-      <c r="G240" s="29"/>
-      <c r="H240" s="29"/>
-      <c r="I240" s="29"/>
-      <c r="J240" s="29"/>
-      <c r="K240" s="29"/>
-      <c r="L240" s="29"/>
-      <c r="M240" s="26"/>
-      <c r="N240" s="26"/>
-      <c r="O240" s="26"/>
-      <c r="P240" s="26"/>
-      <c r="Q240" s="26"/>
-      <c r="R240" s="26"/>
+      <c r="D240" s="26"/>
+      <c r="E240" s="26"/>
+      <c r="F240" s="26"/>
+      <c r="G240" s="26"/>
+      <c r="H240" s="26"/>
+      <c r="I240" s="26"/>
+      <c r="J240" s="26"/>
+      <c r="K240" s="26"/>
+      <c r="L240" s="26"/>
+      <c r="M240" s="23"/>
+      <c r="N240" s="23"/>
+      <c r="O240" s="23"/>
+      <c r="P240" s="23"/>
+      <c r="Q240" s="23"/>
+      <c r="R240" s="23"/>
     </row>
-    <row r="244" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="244" spans="3:30">
       <c r="C244" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="250" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="250" spans="3:30">
       <c r="G250" s="8"/>
     </row>
-    <row r="256" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="256" spans="3:30">
       <c r="F256" s="3"/>
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
@@ -19278,7 +19356,7 @@
       <c r="AC256" s="3"/>
       <c r="AD256" s="3"/>
     </row>
-    <row r="257" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="257" spans="3:30">
       <c r="M257" s="3"/>
       <c r="N257" s="3"/>
       <c r="O257" s="3"/>
@@ -19298,7 +19376,7 @@
       <c r="AC257" s="3"/>
       <c r="AD257" s="3"/>
     </row>
-    <row r="258" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="258" spans="3:30">
       <c r="M258" s="3"/>
       <c r="N258" s="3"/>
       <c r="O258" s="3"/>
@@ -19318,7 +19396,7 @@
       <c r="AC258" s="3"/>
       <c r="AD258" s="3"/>
     </row>
-    <row r="259" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="259" spans="3:30">
       <c r="M259" s="3"/>
       <c r="N259" s="3"/>
       <c r="O259" s="3"/>
@@ -19338,7 +19416,7 @@
       <c r="AC259" s="3"/>
       <c r="AD259" s="3"/>
     </row>
-    <row r="260" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="260" spans="3:30">
       <c r="M260" s="3"/>
       <c r="N260" s="3"/>
       <c r="O260" s="3"/>
@@ -19358,7 +19436,7 @@
       <c r="AC260" s="3"/>
       <c r="AD260" s="3"/>
     </row>
-    <row r="261" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="261" spans="3:30">
       <c r="M261" s="3"/>
       <c r="N261" s="3"/>
       <c r="O261" s="3"/>
@@ -19378,7 +19456,7 @@
       <c r="AC261" s="3"/>
       <c r="AD261" s="3"/>
     </row>
-    <row r="262" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="262" spans="3:30">
       <c r="M262" s="3"/>
       <c r="N262" s="3"/>
       <c r="O262" s="3"/>
@@ -19398,7 +19476,7 @@
       <c r="AC262" s="3"/>
       <c r="AD262" s="3"/>
     </row>
-    <row r="263" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="263" spans="3:30">
       <c r="M263" s="3"/>
       <c r="N263" s="3"/>
       <c r="O263" s="3"/>
@@ -19418,13 +19496,13 @@
       <c r="AC263" s="3"/>
       <c r="AD263" s="3"/>
     </row>
-    <row r="266" spans="3:30" x14ac:dyDescent="0.15">
+    <row r="266" spans="3:30">
       <c r="C266" s="2" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="285" spans="1:81" ht="172.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:81" ht="172.5" customHeight="1"/>
+    <row r="288" spans="1:81">
       <c r="A288" s="1" t="s">
         <v>531</v>
       </c>
@@ -19509,7 +19587,7 @@
       <c r="CB288" s="1"/>
       <c r="CC288" s="1"/>
     </row>
-    <row r="289" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:81">
       <c r="A289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -19590,14 +19668,14 @@
       <c r="CB289" s="3"/>
       <c r="CC289" s="3"/>
     </row>
-    <row r="290" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:81">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:81">
       <c r="C291" s="1" t="s">
         <v>2</v>
       </c>
@@ -19782,7 +19860,7 @@
       </c>
       <c r="CC291" s="4"/>
     </row>
-    <row r="292" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:81">
       <c r="C292" s="1" t="s">
         <v>54</v>
       </c>
@@ -19967,7 +20045,7 @@
       </c>
       <c r="CC292" s="5"/>
     </row>
-    <row r="293" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:81">
       <c r="C293" s="1" t="s">
         <v>57</v>
       </c>
@@ -20152,7 +20230,7 @@
       </c>
       <c r="CC293" s="6"/>
     </row>
-    <row r="294" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:81">
       <c r="C294" s="1" t="s">
         <v>59</v>
       </c>
@@ -20337,7 +20415,7 @@
       </c>
       <c r="CC294" s="6"/>
     </row>
-    <row r="295" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:81">
       <c r="C295" s="1" t="s">
         <v>61</v>
       </c>
@@ -20576,7 +20654,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="296" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:81">
       <c r="C296" s="1" t="s">
         <v>63</v>
       </c>
@@ -20761,12 +20839,12 @@
       </c>
       <c r="CC296" s="5"/>
     </row>
-    <row r="297" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:81">
       <c r="B297" s="2" t="s">
         <v>532</v>
       </c>
       <c r="D297" s="9"/>
-      <c r="E297" s="23" t="s">
+      <c r="E297" s="21" t="s">
         <v>533</v>
       </c>
       <c r="F297" s="12" t="s">
@@ -20946,10 +21024,10 @@
       </c>
       <c r="CC297" s="9"/>
     </row>
-    <row r="299" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:81">
       <c r="E299" s="3"/>
     </row>
-    <row r="300" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:81">
       <c r="D300" s="3">
         <f t="shared" ref="D300:BO300" si="12">LENB(D297)</f>
         <v>0</v>
@@ -21263,7 +21341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:81" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:81">
       <c r="C304" s="3" t="s">
         <v>348</v>
       </c>
@@ -21302,7 +21380,7 @@
       <c r="BZ304" s="3"/>
       <c r="CC304" s="3"/>
     </row>
-    <row r="305" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="305" spans="2:81">
       <c r="C305" s="16" t="s">
         <v>2</v>
       </c>
@@ -21541,7 +21619,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="306" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="306" spans="2:81">
       <c r="C306" s="16" t="s">
         <v>54</v>
       </c>
@@ -21780,7 +21858,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="307" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="307" spans="2:81">
       <c r="C307" s="16" t="s">
         <v>57</v>
       </c>
@@ -22019,7 +22097,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="308" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="308" spans="2:81">
       <c r="C308" s="16" t="s">
         <v>59</v>
       </c>
@@ -22258,7 +22336,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="309" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="309" spans="2:81">
       <c r="C309" s="16" t="s">
         <v>61</v>
       </c>
@@ -22341,7 +22419,7 @@
       <c r="CB309" s="20"/>
       <c r="CC309" s="18"/>
     </row>
-    <row r="310" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="310" spans="2:81">
       <c r="C310" s="16" t="s">
         <v>63</v>
       </c>
@@ -22580,246 +22658,246 @@
         <v>380</v>
       </c>
     </row>
-    <row r="311" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="311" spans="2:81">
       <c r="B311" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="D311" s="22" t="s">
+      <c r="D311" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="E311" s="22" t="s">
+      <c r="E311" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="F311" s="22" t="s">
+      <c r="F311" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="G311" s="22" t="s">
+      <c r="G311" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H311" s="22" t="s">
+      <c r="H311" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="I311" s="22" t="s">
+      <c r="I311" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="J311" s="22" t="s">
+      <c r="J311" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="K311" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="L311" s="22" t="s">
+      <c r="K311" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="L311" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="M311" s="22" t="s">
+      <c r="M311" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="N311" s="22" t="s">
+      <c r="N311" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="O311" s="22" t="s">
+      <c r="O311" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="P311" s="22" t="s">
+      <c r="P311" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="Q311" s="22" t="s">
+      <c r="Q311" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="R311" s="22" t="s">
+      <c r="R311" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="S311" s="22" t="s">
+      <c r="S311" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="T311" s="22" t="s">
+      <c r="T311" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="U311" s="22" t="s">
+      <c r="U311" s="12" t="s">
         <v>538</v>
       </c>
-      <c r="V311" s="22" t="s">
+      <c r="V311" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="W311" s="22" t="s">
+      <c r="W311" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="X311" s="22" t="s">
+      <c r="X311" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="Y311" s="22" t="s">
+      <c r="Y311" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="Z311" s="22" t="s">
+      <c r="Z311" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="AA311" s="22" t="s">
+      <c r="AA311" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="AB311" s="22" t="s">
+      <c r="AB311" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="AC311" s="22" t="s">
+      <c r="AC311" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="AD311" s="22" t="s">
+      <c r="AD311" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="AE311" s="22" t="s">
+      <c r="AE311" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="AF311" s="22" t="s">
+      <c r="AF311" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="AG311" s="22" t="s">
+      <c r="AG311" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="AH311" s="22" t="s">
+      <c r="AH311" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="AI311" s="22" t="s">
+      <c r="AI311" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="AJ311" s="22" t="s">
+      <c r="AJ311" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="AK311" s="22" t="s">
+      <c r="AK311" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="AL311" s="22" t="s">
+      <c r="AL311" s="12" t="s">
         <v>402</v>
       </c>
-      <c r="AM311" s="22" t="s">
+      <c r="AM311" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="AN311" s="22" t="s">
+      <c r="AN311" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="AO311" s="22" t="s">
+      <c r="AO311" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="AP311" s="22" t="s">
+      <c r="AP311" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="AQ311" s="22" t="s">
+      <c r="AQ311" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="AR311" s="22" t="s">
+      <c r="AR311" s="12" t="s">
         <v>406</v>
       </c>
-      <c r="AS311" s="22" t="s">
+      <c r="AS311" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="AT311" s="22" t="s">
+      <c r="AT311" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="AU311" s="22" t="s">
+      <c r="AU311" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="AV311" s="22" t="s">
+      <c r="AV311" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="AW311" s="22" t="s">
+      <c r="AW311" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="AX311" s="22" t="s">
+      <c r="AX311" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="AY311" s="22" t="s">
+      <c r="AY311" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="AZ311" s="22" t="s">
+      <c r="AZ311" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="BA311" s="22" t="s">
+      <c r="BA311" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="BB311" s="22" t="s">
+      <c r="BB311" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="BC311" s="22" t="s">
+      <c r="BC311" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="BD311" s="22" t="s">
+      <c r="BD311" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="BE311" s="22" t="s">
+      <c r="BE311" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="BF311" s="22" t="s">
+      <c r="BF311" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="BG311" s="22" t="s">
+      <c r="BG311" s="12" t="s">
         <v>565</v>
       </c>
-      <c r="BH311" s="22" t="s">
+      <c r="BH311" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="BI311" s="22" t="s">
+      <c r="BI311" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="BJ311" s="22" t="s">
+      <c r="BJ311" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="BK311" s="22" t="s">
+      <c r="BK311" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="BL311" s="22" t="s">
+      <c r="BL311" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="BM311" s="22" t="s">
+      <c r="BM311" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="BN311" s="22" t="s">
+      <c r="BN311" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="BO311" s="22" t="s">
+      <c r="BO311" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="BP311" s="22" t="s">
+      <c r="BP311" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="BQ311" s="22" t="s">
+      <c r="BQ311" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="BR311" s="22" t="s">
+      <c r="BR311" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="BS311" s="22" t="s">
+      <c r="BS311" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="BT311" s="22" t="s">
+      <c r="BT311" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="BU311" s="22" t="s">
+      <c r="BU311" s="12" t="s">
         <v>555</v>
       </c>
-      <c r="BV311" s="22" t="s">
+      <c r="BV311" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="BW311" s="22" t="s">
+      <c r="BW311" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="BX311" s="22" t="s">
+      <c r="BX311" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="BY311" s="22" t="s">
+      <c r="BY311" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="BZ311" s="22" t="s">
+      <c r="BZ311" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="CA311" s="22" t="s">
+      <c r="CA311" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="CB311" s="22" t="s">
+      <c r="CB311" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="CC311" s="22" t="s">
+      <c r="CC311" s="12" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="314" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="314" spans="2:81">
       <c r="D314" s="3">
         <f t="shared" ref="D314:BO314" si="14">LENB(D311)</f>
         <v>4</v>
@@ -22858,7 +22936,7 @@
       </c>
       <c r="M314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="N314" s="3">
         <f t="shared" si="14"/>
@@ -22882,11 +22960,11 @@
       </c>
       <c r="S314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="T314" s="3">
         <f t="shared" si="14"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U314" s="3">
         <f t="shared" si="14"/>
@@ -22906,7 +22984,7 @@
       </c>
       <c r="Y314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="Z314" s="3">
         <f t="shared" si="14"/>
@@ -22918,11 +22996,11 @@
       </c>
       <c r="AB314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AC314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AD314" s="3">
         <f t="shared" si="14"/>
@@ -22974,7 +23052,7 @@
       </c>
       <c r="AP314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AQ314" s="3">
         <f t="shared" si="14"/>
@@ -22982,15 +23060,15 @@
       </c>
       <c r="AR314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AS314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AT314" s="3">
         <f t="shared" si="14"/>
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AU314" s="3">
         <f t="shared" si="14"/>
@@ -22998,7 +23076,7 @@
       </c>
       <c r="AV314" s="3">
         <f t="shared" si="14"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AW314" s="3">
         <f t="shared" si="14"/>
@@ -23054,11 +23132,11 @@
       </c>
       <c r="BJ314" s="3">
         <f t="shared" si="14"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BK314" s="3">
         <f t="shared" si="14"/>
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BL314" s="3">
         <f t="shared" si="14"/>
@@ -23094,7 +23172,7 @@
       </c>
       <c r="BT314" s="3">
         <f t="shared" si="15"/>
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="BU314" s="3">
         <f t="shared" si="15"/>
@@ -23133,22 +23211,22 @@
         <v>56</v>
       </c>
     </row>
-    <row r="319" spans="2:81" x14ac:dyDescent="0.15">
+    <row r="319" spans="2:81">
       <c r="C319" s="2" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="337" spans="3:3">
       <c r="C337" s="2" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="357" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="357" spans="3:3">
       <c r="C357" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="375" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="375" spans="3:3">
       <c r="C375" s="2" t="s">
         <v>530</v>
       </c>
@@ -23160,12 +23238,12 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="BJ12" r:id="rId1"/>
-    <hyperlink ref="BO12" r:id="rId2"/>
-    <hyperlink ref="BG12" r:id="rId3" display="¥¥¥¥¥¥¥¥¥¥¥¥¥¥"/>
-    <hyperlink ref="BO38" r:id="rId4"/>
-    <hyperlink ref="BG38" r:id="rId5" display="¥¥¥¥¥"/>
-    <hyperlink ref="BJ38" r:id="rId6" display="!$#^@&amp;(@)$&amp;&amp;#^%&amp;#($))))$#"/>
+    <hyperlink ref="BJ12" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="BO12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="BG12" r:id="rId3" display="¥¥¥¥¥¥¥¥¥¥¥¥¥¥" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="BO38" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="BG38" r:id="rId5" display="¥¥¥¥¥" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="BJ38" r:id="rId6" display="!$#^@&amp;(@)$&amp;&amp;#^%&amp;#($))))$#" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="10" fitToHeight="0" orientation="landscape" r:id="rId7"/>
